--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -458,10 +458,10 @@
         <v>כל הטקסטים עוברים לעברית בלחיצה</v>
       </c>
       <c r="C4" t="str">
-        <v>⚠️</v>
+        <v>✅</v>
       </c>
       <c r="D4" t="str">
-        <v>חלקי — פערי i18n פתוחים: urgency, frequency, SuggestedAction, About, HolidayDetail</v>
+        <v>iteration 12 השלים: urgency/frequency/SuggestedAction/HolidayDetail/AboutScreen — כל הטקסטים עוברים ב-t()</v>
       </c>
     </row>
     <row r="5">
@@ -500,10 +500,10 @@
         <v>כפתור חזרה — aria-label בעברית</v>
       </c>
       <c r="C7" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D7" t="str">
-        <v>FINDING 25A פתוח — aria-label="Go back" קשיח ב-PageHeader; דרוש מפתח go_back ב-i18n</v>
+        <v>FINDING 25A תוקן iteration 12 — go_back נוסף ל-i18n; PageHeader משתמש ב-t('go_back')</v>
       </c>
     </row>
     <row r="8">
@@ -514,10 +514,10 @@
         <v>מסך About — כל התוכן בעברית</v>
       </c>
       <c r="C8" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D8" t="str">
-        <v>FINDING 27 פתוח — VALUES/TECH arrays + mission paragraph כולם EN קשיח; 16 מפתחות חסרים</v>
+        <v>FINDING 27 תוקן iteration 12 — 19 מפתחות about_* נוספו ל-i18n; AboutScreen משתמש ב-t() לכל תוכן EN</v>
       </c>
     </row>
     <row r="9">
@@ -528,10 +528,10 @@
         <v>urgencyLevel — תרגום (קריטי/גבוה/בינוני/נמוך)</v>
       </c>
       <c r="C9" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D9" t="str">
-        <v>FINDING 20 פתוח — score.urgencyLevel מוצג ישירות ב-JSX; דרוש urgency_critical/high/medium/low</v>
+        <v>FINDING 20 תוקן iteration 12 — urgency_critical/high/medium/low נוספו ל-i18n; ContactDetailScreen משתמש ב-t()</v>
       </c>
     </row>
     <row r="10">
@@ -542,10 +542,10 @@
         <v>interactionFrequency — תרגום (יומי/שבועי/חודשי/רבעוני)</v>
       </c>
       <c r="C10" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D10" t="str">
-        <v>FINDING 20 פתוח — capitalize-first ידני, לא עובר t(); דרוש freq_daily/weekly/monthly/quarterly</v>
+        <v>FINDING 20 תוקן iteration 12 — freq_* קיים ל-7 ערכים; ContactDetailScreen משתמש ב-t() במקום capitalize-first</v>
       </c>
     </row>
     <row r="11">
@@ -556,10 +556,10 @@
         <v>תוויות SuggestedAction בעברית (מסך פרטי קשר)</v>
       </c>
       <c r="C11" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D11" t="str">
-        <v>FINDING 23 פתוח — scoringSystem.ts מייצר EN קשיח; תרגום צריך להיות ב-ContactDetailScreen עם t()</v>
+        <v>FINDING 23 תוקן iteration 12 — action_* keys נוספו ל-i18n; ContactDetailScreen מחשב translatedActionLabel לפי type</v>
       </c>
     </row>
     <row r="12">
@@ -570,10 +570,10 @@
         <v>badge "★ ראשי" בפרטי חג</v>
       </c>
       <c r="C12" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D12" t="str">
-        <v>FINDING 28A פתוח — ★ Major קשיח; חסר מפתח holiday_major בשתי שפות</v>
+        <v>FINDING 28A תוקן iteration 12 — holiday_major + holiday_moreContacts נוספו ל-i18n; HolidayDetailScreen משתמש ב-t()</v>
       </c>
     </row>
     <row r="13">
@@ -724,10 +724,10 @@
         <v>badge urgencyLevel מוצג בכרטיס איש קשר</v>
       </c>
       <c r="C23" t="str">
-        <v>⚠️</v>
+        <v>✅</v>
       </c>
       <c r="D23" t="str">
-        <v>FINDING 20 פתוח — badge מוצג אבל ערכי urgencyLevel בEN קשיח (critical/high/medium/low)</v>
+        <v>FINDING 20 תוקן iteration 12 — urgency_* keys ב-i18n; ContactDetailScreen מציג t('urgency_critical') וכו'</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         <v>SuggestedAction label נראה ב-ContactDetail</v>
       </c>
       <c r="C24" t="str">
-        <v>⚠️</v>
+        <v>✅</v>
       </c>
       <c r="D24" t="str">
-        <v>FINDING 23 פתוח — label מוצג אבל מחרוזות EN קשיחות מ-scoringSystem.ts</v>
+        <v>FINDING 23 תוקן iteration 12 — translatedActionLabel ב-ContactDetailScreen; label מתורגם לפי action.type</v>
       </c>
     </row>
     <row r="25">
@@ -780,10 +780,10 @@
         <v>interactionFrequency מוצג בפרטי קשר</v>
       </c>
       <c r="C27" t="str">
-        <v>⚠️</v>
+        <v>✅</v>
       </c>
       <c r="D27" t="str">
-        <v>FINDING 20 פתוח — מוצג אבל charAt(0).toUpperCase() ידני, לא t(); תמיד EN</v>
+        <v>FINDING 20 תוקן iteration 12 — ContactDetailScreen משתמש ב-t('freq_monthly') וכו' במקום charAt(0).toUpperCase()</v>
       </c>
     </row>
     <row r="28">
@@ -1032,10 +1032,10 @@
         <v>DST birthday bug — getBirthdayDaysUntil</v>
       </c>
       <c r="C45" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D45" t="str">
-        <v>BUG-020 פתוח — Math.floor(ms/86400000) יחזיר -1 ביום שינוי שעון; דרוש differenceInCalendarDays</v>
+        <v>BUG-020 תוקן iteration 12 — getBirthdayDaysUntil משתמש ב-differenceInCalendarDays מ-date-fns</v>
       </c>
     </row>
     <row r="46">
@@ -1046,10 +1046,10 @@
         <v>key={i} ב-ImportContactsScreen rows</v>
       </c>
       <c r="C46" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D46" t="str">
-        <v>BUG-021 פתוח — key={i} על שורות preview ועל רשימת שגיאות ב-ImportContactsScreen</v>
+        <v>BUG-021 — key={i} טופל: שורות preview משתמשות ב-key={`row-${i}`}, שגיאות ב-key={e} (מחרוזת ייחודית)</v>
       </c>
     </row>
     <row r="47">
@@ -1060,10 +1060,10 @@
         <v>setImporting(false) לא ב-finally</v>
       </c>
       <c r="C47" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D47" t="str">
-        <v>FINDING 60 פתוח — setImporting(false) אחרי try/catch ולא ב-finally; Import button עלול להישאר נעול</v>
+        <v>FINDING 60 תוקן iteration 12 — setImporting(false) הועבר ל-finally block</v>
       </c>
     </row>
     <row r="48">
@@ -1088,10 +1088,10 @@
         <v>ErrorBoundary מונע מסך לבן על crash</v>
       </c>
       <c r="C49" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D49" t="str">
-        <v>FINDING 14 פתוח — אין ErrorBoundary; crash בכל מסך → מסך לבן; קריטי ב-Capacitor (אין כפתור רענון)</v>
+        <v>App.tsx שורות 9-38 — ErrorBoundary class component מיושם; Hebrew error UI עם כפתור רענון; wraps AppShell</v>
       </c>
     </row>
     <row r="50">
@@ -1130,10 +1130,10 @@
         <v>כרטיסי Dashboard/Groups — ניגשים למקלדת (div→button)</v>
       </c>
       <c r="C52" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D52" t="str">
-        <v>FINDING 67 פתוח — Dashboard (שורות 131,147) + GroupsScreen (שורה 132): div onClick ללא tabindex/role</v>
+        <v>FINDING 67 תוקן iteration 12 — Dashboard today-highlight cards + GroupsScreen group cards הומרו ל-&lt;button type=button&gt;</v>
       </c>
     </row>
     <row r="53">
@@ -1144,10 +1144,10 @@
         <v>.btn — טבעת focus-visible</v>
       </c>
       <c r="C53" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D53" t="str">
-        <v>FINDING 69 פתוח — .btn חסר :focus-visible; כפתורים ראשיים מסתמכים על UA default בלבד</v>
+        <v>FINDING 69 תוקן iteration 12 — .btn:focus-visible { outline: 2px solid var(--color-primary); outline-offset: 2px; } נוסף ל-index.css</v>
       </c>
     </row>
     <row r="54">
@@ -1172,10 +1172,10 @@
         <v>כפתור סגירת Modal — aria-label בעברית</v>
       </c>
       <c r="C55" t="str">
-        <v>❌</v>
+        <v>✅</v>
       </c>
       <c r="D55" t="str">
-        <v>FINDING 30B פתוח — aria-label="Close" קשיח; מפתח close קיים ב-i18n אבל Modal לא משתמש ב-useT()</v>
+        <v>FINDING 30B תוקן iteration 12 — Modal.tsx מייבא useT(); aria-label={t('close')} בעברית/אנגלית לפי שפה</v>
       </c>
     </row>
     <row r="56">

--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D85</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D85"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -1332,10 +1332,276 @@
         <v>src/integrations/payment/payme.ts + ai/claudeClient.ts — stubs מוכנים; BUG-030 תוקן</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>🔗</v>
+      </c>
+      <c r="B67" t="str">
+        <v>DeviceContactsScreen — ייבוא מאנשי קשר של המכשיר (Capacitor)</v>
+      </c>
+      <c r="C67" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D67" t="str">
+        <v>BL-030 Sprint 3: DeviceContactsScreen with @capacitor-community/contacts; consent/permission/list/import flow; phone dedup; Capacitor.isNativePlatform() guard; Premium route /device-contacts; import shortcut in ImportContactsScreen</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>🚀</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Sprint 4 — ייצוא / גיבוי / נגישות / ספרינט</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>🚀</v>
+      </c>
+      <c r="B69" t="str">
+        <v>celebrationType שדה בקשר — סינון חגים לפי סוג חגיגה</v>
+      </c>
+      <c r="C69" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D69" t="str">
+        <v>BL-026 Sprint 3: CelebrationType field added to Contact; select in ContactForm Cultural section; CELEBRATION_TO_RELIGION map in scoringSystem.ts; 10 i18n keys EN+HE</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>🚀</v>
+      </c>
+      <c r="B70" t="str">
+        <v>התראה לאיש קשר שלא דיברו עמו 45 יום + יום הולדת קרוב</v>
+      </c>
+      <c r="C70" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D70" t="str">
+        <v>BL-023 Sprint 3: Overdue contact notification added to notificationService.ts (45-day threshold); skips if birthday reminder within 7d; dedup via nm_notif_sent; EN+HE keys</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>🚀</v>
+      </c>
+      <c r="B71" t="str">
+        <v>BUG-043: נקודות חגים מרובי-ימים (סוכות/חנוכה) בלוח שנה</v>
+      </c>
+      <c r="C71" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D71" t="str">
+        <v>BUG-043: CalendarScreen getHolidaysForDay now uses numeric YYYYMMDD range; all days of Sukkot/Hanukkah/multi-day holidays show dot</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>🚀</v>
+      </c>
+      <c r="B72" t="str">
+        <v>BUG-044: סוכות 2026 נוסף ל-holidays.ts</v>
+      </c>
+      <c r="C72" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D72" t="str">
+        <v>BUG-044: sukkot-2026 added to holidays.ts (Sep 25–Oct 2, 2026); calendar now shows Sukkot for 2026</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>🚀</v>
+      </c>
+      <c r="B73" t="str">
+        <v>BL-025: ייצוא אנשי קשר ל-CSV (Premium)</v>
+      </c>
+      <c r="C73" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D73" t="str">
+        <v>BL-025 Sprint 4: exportService.ts עם PapaParse + BOM; כפתור ייצוא CSV ב-SettingsScreen Premium Features; exportDone feedback 2.5s; EN+HE i18n keys</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>🚀</v>
+      </c>
+      <c r="B74" t="str">
+        <v>BL-029: כל כפתורי icon-only ≥ 48×48px (WCAG 2.5.5)</v>
+      </c>
+      <c r="C74" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D74" t="str">
+        <v>BL-029 Sprint 4 WCAG 2.5.5: 9 כפתורי icon-only עודכנו ל-min-w/h-[48px]; Navigation, ContactForm, ContactDetail, GroupsScreen, GreetingEditor, Modal, HolidayDetail, BirthdayGreetingEditor</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>🚀</v>
+      </c>
+      <c r="B75" t="str">
+        <v>BL-024: haptic feedback — שמירת קשר / שליחת ברכה / קופון</v>
+      </c>
+      <c r="C75" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D75" t="str">
+        <v>BL-024 Sprint 4: hapticService.ts עם Light/Medium/Success/Error; מחובר ל-save contact, send greeting (ChannelPicker), coupon success/error; no-op בדפדפן</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>🚀</v>
+      </c>
+      <c r="B76" t="str">
+        <v>BL-034: גיבוי ושחזור JSON (ייצוא/ייבוא כל הנתונים)</v>
+      </c>
+      <c r="C76" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D76" t="str">
+        <v>BL-034 Sprint 4: exportBackupJSON/importBackupJSON ב-storageService.ts; UI ב-SettingsScreen Premium Features; restore reload אוטומטי; error state 3s</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>🚀</v>
+      </c>
+      <c r="B77" t="str">
+        <v>BL-035: זיהוי קשר כפול — שם זהה או מספר טלפון זהה</v>
+      </c>
+      <c r="C77" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D77" t="str">
+        <v>BL-035 Sprint 4: findDuplicate() בודק שם exact + phone ≥7 ספרות; Modal אזהרה עם שם הכפול; Save Anyway / Cancel; לא חוסם עריכה קיימת</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>🗂️</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Sprint 5 — ייבוא / קבוצות / ניווט</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>🗂️</v>
+      </c>
+      <c r="B79" t="str">
+        <v>BL-046: כפתור ייבוא ב-ContactsScreen (Premium) + empty-state shortcut</v>
+      </c>
+      <c r="C79" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D79" t="str">
+        <v>BL-046 Sprint 5: FileUp icon ב-ContactsScreen header (Premium only) + empty-state shortcut → /import</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>🗂️</v>
+      </c>
+      <c r="B80" t="str">
+        <v>BL-047: תוויות CSV בלבד ב-ImportContactsScreen</v>
+      </c>
+      <c r="C80" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D80" t="str">
+        <v>BL-047 Sprint 5: accept='.csv' + תווית 📄 CSV badge + i18n key import_csvOnly ב-ImportContactsScreen</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>🗂️</v>
+      </c>
+      <c r="B81" t="str">
+        <v>BL-048: כפתור import מהמכשיר כ-Blue gradient card</v>
+      </c>
+      <c r="C81" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D81" t="str">
+        <v>BL-048 Sprint 5: כפתור device contacts כ-Blue gradient card עם Smartphone icon + arrow; divider 'or upload CSV' ב-ImportContactsScreen</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>🗂️</v>
+      </c>
+      <c r="B82" t="str">
+        <v>BL-049: מחוון tab פעיל — נקודה / אייקון גדול / טקסט עבה</v>
+      </c>
+      <c r="C82" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D82" t="str">
+        <v>BL-049 Sprint 5: dot indicator + icon 22px + fontWeight 800 primary color label על tab פעיל ב-BottomNav; background glow</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>🗂️</v>
+      </c>
+      <c r="B83" t="str">
+        <v>BL-052: purpose selector בקבוצה + הצעות חגים אוטומטיות</v>
+      </c>
+      <c r="C83" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D83" t="str">
+        <v>BL-052 Sprint 5: GroupPurpose type + purpose field ב-Group; SUGGESTED_BASES lookup; applyPurpose(); purpose pills + ✦ badge על holidays מוצעים ב-GroupsScreen</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>🗂️</v>
+      </c>
+      <c r="B84" t="str">
+        <v>BL-050: שיוך אנשי קשר מיובאים לקבוצה בשלב done</v>
+      </c>
+      <c r="C84" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D84" t="str">
+        <v>BL-050 Sprint 5: group assignment UI בשלב done של ImportContactsScreen; select + assign button; Set merge; groupAssigned success state</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>🗂️</v>
+      </c>
+      <c r="B85" t="str">
+        <v>BL-051: הורדת תבנית CSV עם כותרות עבריות</v>
+      </c>
+      <c r="C85" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D85" t="str">
+        <v>BL-051 Sprint 5: downloadCSVTemplate() — CSV Blob עם BOM + עמודות עבריות + שורת דוגמה; כפתור בשלב upload</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D66"/>
+  <autoFilter ref="A1:D85"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D85"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D92</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D92"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -1598,10 +1598,108 @@
         <v>BL-051 Sprint 5: downloadCSVTemplate() — CSV Blob עם BOM + עמודות עבריות + שורת דוגמה; כפתור בשלב upload</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Sprint 6 — תיקוני איכות / Findings 31/49/75/76/84/85/86</v>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B87" t="str">
+        <v>FINDING 86: SUGGESTED_BASES חולץ ל-src/data/groupSuggestions.ts</v>
+      </c>
+      <c r="C87" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D87" t="str">
+        <v>FINDING 86 Sprint 6: SUGGESTED_BASES חולץ ל-src/data/groupSuggestions.ts; GroupsScreen מייבא ממנו</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B88" t="str">
+        <v>FINDING 75/87: applyPurpose מנקה holidays של קטגוריה קודמת</v>
+      </c>
+      <c r="C88" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D88" t="str">
+        <v>FINDING 75/87 Sprint 6: applyPurpose() מנקה ה-holidays מהקטגוריה הישנה לפני הוספת החדשים — אין הצטברות של holidays לא רלוונטיים</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B89" t="str">
+        <v>FINDING 31: MediaAttachmentPicker — "1:00" מיותר הוסר</v>
+      </c>
+      <c r="C89" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D89" t="str">
+        <v>FINDING 31 Sprint 6: MediaAttachmentPicker — הוסרו המילים " 1:00" המיותרות; ממשק ההקלטה מציג רק t(media_record_limit)</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B90" t="str">
+        <v>FINDING 49: Send to Group מנווט ל-/greeting עם contactId+holidayId</v>
+      </c>
+      <c r="C90" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D90" t="str">
+        <v>FINDING 49 Sprint 6: כפתור Send to Group מנווט ל-/greeting עם contactId + holidayId של איש הקשר הראשון בקבוצה</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B91" t="str">
+        <v>FINDING 76/81: findDuplicate בודקת עריכה + self-exclusion</v>
+      </c>
+      <c r="C91" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D91" t="str">
+        <v>FINDING 76/81 Sprint 6: findDuplicate() בודקת גם עת עריכה; self-exclusion לפי contact.id; handleSave ללא גייט isNew</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B92" t="str">
+        <v>FINDING 84/85: group assign try/catch + hidden when 0 imported</v>
+      </c>
+      <c r="C92" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D92" t="str">
+        <v>FINDING 84/85 Sprint 6: כרטיס שיוך קבוצה מוסתר כשאין קשרים מיובאים; כפתור שיוך עם try/catch + הודעת שגיאה בעברית</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D85"/>
+  <autoFilter ref="A1:D92"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D85"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D92"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D101</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D101"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -1696,10 +1696,136 @@
         <v>FINDING 84/85 Sprint 6: כרטיס שיוך קבוצה מוסתר כשאין קשרים מיובאים; כפתור שיוך עם try/catch + הודעת שגיאה בעברית</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>🎮</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Sprint 7 — Demo Mode (BL-036) + i18n BirthdayCenterScreen + מחרוזות נגישות</v>
+      </c>
+      <c r="C93" t="str">
+        <v/>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>🎮</v>
+      </c>
+      <c r="B94" t="str">
+        <v>BL-036: src/data/demoData.ts — 6 אנשי קשר + 2 קבוצות דוגמה</v>
+      </c>
+      <c r="C94" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D94" t="str">
+        <v>BL-036 Sprint 7: src/data/demoData.ts נוצר — 6 אנשי קשר דוגמה מגוונים + 2 קבוצות</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>🎮</v>
+      </c>
+      <c r="B95" t="str">
+        <v>BL-036: isDemoMode/enableDemoMode/clearDemoMode — ניתוב ל-nm_demo_* keys</v>
+      </c>
+      <c r="C95" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D95" t="str">
+        <v>BL-036 Sprint 7: isDemoMode()/enableDemoMode()/clearDemoMode() ב-storageService; getContacts/saveContacts/getGroups/saveGroups מנותבים לפי isDemoMode</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>🎮</v>
+      </c>
+      <c r="B96" t="str">
+        <v>BL-036: כפתור Try Demo ב-Onboarding + DemoBanner + Exit בהגדרות</v>
+      </c>
+      <c r="C96" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D96" t="str">
+        <v>BL-036 Sprint 7: כפתור 'נסה הדגמה' בשקף האחרון של Onboarding; DemoBanner בפסקה העליונה; כרטיס 'צא ממצב הדגמה' בהגדרות</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>🎮</v>
+      </c>
+      <c r="B97" t="str">
+        <v>BL-036: נתוני משתמש אמיתיים לא נפגעים במצב הדגמה</v>
+      </c>
+      <c r="C97" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D97" t="str">
+        <v>BL-036 Sprint 7: נתוני משתמש אמיתיים לא נפגעים — מצב הדגמה משתמש ב-nm_demo_* keys בלבד; clearDemoMode() מוחק רק אותם</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>🎮</v>
+      </c>
+      <c r="B98" t="str">
+        <v>i18n: 7 מחרוזות BirthdayCenterScreen ב-t() — hero, subtitle, count, noneTracked, badge, itsTheirBirthday, day/days</v>
+      </c>
+      <c r="C98" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Sprint 7 i18n: 7 מחרוזות קשיחות ב-BirthdayCenterScreen הוחלפו ב-t() — hero title, subtitle, contactCount, noneTracked, todayBadge, itsTheirBirthday, day/days</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>🎮</v>
+      </c>
+      <c r="B99" t="str">
+        <v>i18n: contacts_addContact / calendar_prevMonth+nextMonth / groups_searchHolidays / dashboard_isTomorrow+prepareGreetings / greeting_copy</v>
+      </c>
+      <c r="C99" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Sprint 7 i18n: contacts_addContact (Dashboard FAB + EmptyState + ContactsScreen FAB), calendar_prevMonth/nextMonth, groups_searchHolidays, dashboard_isTomorrow, dashboard_prepareGreetings, greeting_copy (HolidayDetailScreen)</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>🎮</v>
+      </c>
+      <c r="B100" t="str">
+        <v>i18n: מפתחות demo_banner/loadData/clear/clearConfirm/cleared ב-EN+HE</v>
+      </c>
+      <c r="C100" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Sprint 7 i18n: מפתחות demo_banner/loadData/clear/clearConfirm/cleared EN+HE — 5 מפתחות חדשים</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>🎮</v>
+      </c>
+      <c r="B101" t="str">
+        <v>QA end-to-end: Onboarding → Try Demo → DemoBanner → Settings exit; RTL; בידוד נתונים</v>
+      </c>
+      <c r="C101" t="str">
+        <v>☐</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Sprint 7 QA: בדיקת מצב הדגמה end-to-end — Onboarding → Try Demo → DemoBanner → Settings exit; RTL Hebrew; בידוד נתונים</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D92"/>
+  <autoFilter ref="A1:D101"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D107</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D107"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -1822,10 +1822,94 @@
         <v>Sprint 7 QA: בדיקת מצב הדגמה end-to-end — Onboarding → Try Demo → DemoBanner → Settings exit; RTL Hebrew; בידוד נתונים</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Sprint 8 — Stability · Accessibility · RTL/Hebrew Correctness (FINDING 28D, 29A/B/C)</v>
+      </c>
+      <c r="C102" t="str">
+        <v/>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B103" t="str">
+        <v>FINDING 28D: dir(langCode) ב-i18n; GreetingRow dir attribute מחושב לפי langCode</v>
+      </c>
+      <c r="C103" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Sprint 8 FINDING 28D: dir(langCode) נוסף ל-src/i18n/index.ts; GreetingRow משתמשת ב-langCode prop במקום השוואת מחרוזת; build+lint עבר</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B104" t="str">
+        <v>FINDING 29A: תווית Avatar Color מוחלפת ב-t(contactForm_avatarColor) — EN/HE</v>
+      </c>
+      <c r="C104" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Sprint 8 FINDING 29A: תווית 'Avatar Color' מוחלפת ב-t('contactForm_avatarColor') — EN/HE תוקן</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B105" t="str">
+        <v>FINDING 29B: aria-label על כפתור Auto gradient — WCAG 4.1.2 תוקן</v>
+      </c>
+      <c r="C105" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Sprint 8 FINDING 29B: כפתור 'Auto gradient' — title הוחלף ב-aria-label={t('contactForm_autoGradient')}; WCAG 4.1.2 מתוקן</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B106" t="str">
+        <v>FINDING 29C: PremiumFeaturePrompt feature — t(premium_feat_birthday_fields) כבר קיים</v>
+      </c>
+      <c r="C106" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Sprint 8 FINDING 29C: PremiumFeaturePrompt feature כבר שימשה ב-t('premium_feat_birthday_fields') — לא נדרש שינוי</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Sprint 8 QA: build נקי + lint נקי אחרי כל תיקוני Sprint 8</v>
+      </c>
+      <c r="C107" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Sprint 8 QA: build עבר ו-lint נקי אחרי כל תיקוני Sprint 8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D101"/>
+  <autoFilter ref="A1:D107"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D107"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D115</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D115"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -1906,10 +1906,122 @@
         <v>Sprint 8 QA: build עבר ו-lint נקי אחרי כל תיקוני Sprint 8</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>💳</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Sprint 9 — Holiday Reminders (BL-059) + PayMe Payment UI (BL-032)</v>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>💳</v>
+      </c>
+      <c r="B109" t="str">
+        <v>BL-059: reminderService — getReminderSettings/saveReminderSettings/hasBeenReminded/markReminded</v>
+      </c>
+      <c r="C109" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D109" t="str">
+        <v>BL-059: reminderService.ts — getReminderSettings/saveReminderSettings/hasBeenReminded/markReminded; build+lint</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>💳</v>
+      </c>
+      <c r="B110" t="str">
+        <v>BL-059: HolidayRemindersScreen — toggle, days ahead, 4 channels, upcoming list, save</v>
+      </c>
+      <c r="C110" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D110" t="str">
+        <v>BL-059: HolidayRemindersScreen — premium gate; master toggle; days ahead 1/3/7; Push/SMS/Email/WhatsApp channels; provider disclaimer; upcoming pairs list; save bar</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>💳</v>
+      </c>
+      <c r="B111" t="str">
+        <v>BL-059: free users see PremiumFeaturePrompt; premium users see full config</v>
+      </c>
+      <c r="C111" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D111" t="str">
+        <v>BL-059: free users see PremiumFeaturePrompt on /reminders; premium users see full config</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>💳</v>
+      </c>
+      <c r="B112" t="str">
+        <v>BL-059: dedup — אותו contactId:holidayId לא יקבל תזכורת פעמיים באותו יום</v>
+      </c>
+      <c r="C112" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D112" t="str">
+        <v>BL-059: dedup via nm_holiday_reminder_sent key (contactId:holidayId per day)</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>💳</v>
+      </c>
+      <c r="B113" t="str">
+        <v>BL-032: PaymeScreen — plan picker, form, CTA, error handling, already-premium state</v>
+      </c>
+      <c r="C113" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D113" t="str">
+        <v>BL-032: PaymeScreen — plan picker monthly/annual; name+email form; Pay with PayMe CTA; error handling (stub throws); disclaimer; already-premium state</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>💳</v>
+      </c>
+      <c r="B114" t="str">
+        <v>BL-032: UpgradeScreen → /payment; SettingsScreen → Holiday Reminders entry</v>
+      </c>
+      <c r="C114" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D114" t="str">
+        <v>BL-032: UpgradeScreen כפתור 'שלם עם PayMe' מנווט ל-/payment; SettingsScreen → Holiday Reminders entry ב-Premium Features</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>💳</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Sprint 9 QA: build נקי + lint נקי; שני מסכים נטענים כ-lazy chunks</v>
+      </c>
+      <c r="C115" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Sprint 9 QA: build נקי + lint נקי; HolidayRemindersScreen ו-PaymeScreen נטענים כ-lazy chunks נפרדים</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D107"/>
+  <autoFilter ref="A1:D115"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D107"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D115"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D122</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D122"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2018,10 +2018,108 @@
         <v>Sprint 9 QA: build נקי + lint נקי; HolidayRemindersScreen ו-PaymeScreen נטענים כ-lazy chunks נפרדים</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>🤖</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Sprint 10 — AI Suggestions MVP (BL-033) + Secular/National Dates (BL-060)</v>
+      </c>
+      <c r="C116" t="str">
+        <v/>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>🤖</v>
+      </c>
+      <c r="B117" t="str">
+        <v>BL-033: aiSuggestionsService — 3 options per tone×holiday×lang (casual/professional/vip, EN/HE/AR)</v>
+      </c>
+      <c r="C117" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D117" t="str">
+        <v>BL-033: aiSuggestionsService.ts — getAISuggestions מחזיר 3 אפשרויות שונות לפי tone×holiday×lang; casual/professional/vip; EN/HE/AR</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>🤖</v>
+      </c>
+      <c r="B118" t="str">
+        <v>BL-033: AI Suggestions button in GreetingEditorScreen — premium gate (PRO badge → /upgrade for free users)</v>
+      </c>
+      <c r="C118" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D118" t="str">
+        <v>BL-033: כפתור AI Suggestions ב-GreetingEditorScreen — premium gate (PRO badge → /upgrade); premium users ← 400ms delay → 3 options panel</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>🤖</v>
+      </c>
+      <c r="B119" t="str">
+        <v>BL-033: selecting a suggestion populates message field; panel closes; Use this button per option</v>
+      </c>
+      <c r="C119" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D119" t="str">
+        <v>BL-033: בחירת suggestion ממלאת את message field ומסתירה את הפאנל; כפתור Use this לכל אפשרות</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>🤖</v>
+      </c>
+      <c r="B120" t="str">
+        <v>BL-033: premium user sees purple AI button; generates 3 distinct options with 400ms delay</v>
+      </c>
+      <c r="C120" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D120" t="str">
+        <v>BL-033: HA לא premium — כפתור ממוסגר עם PRO badge; לחיצה → /upgrade; premium — כפתור סגול פעיל</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>🤖</v>
+      </c>
+      <c r="B121" t="str">
+        <v>BL-060: 5 secular/national dates added — Holocaust Intl (Jan 27), Yom HaShoah, Yom HaZikaron, US Memorial Day, US Independence Day</v>
+      </c>
+      <c r="C121" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D121" t="str">
+        <v>BL-060: 5 תאריכים חילוניים/לאומיים נוספו להוליידייס: Holocaust Remembrance Intl (Jan 27), Yom HaShoah (27 Nisan), Yom HaZikaron (4 Iyar), US Memorial Day (May 25), US Independence Day (Jul 4)</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>🤖</v>
+      </c>
+      <c r="B122" t="str">
+        <v>BL-060: all new dates under religion: Secular; greetings EN+HE; sensitivity notes on memorial days; build+lint pass</v>
+      </c>
+      <c r="C122" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D122" t="str">
+        <v>BL-060: כל התאריכים החדשים עם religion: Secular; ברכות EN+HE; הערות רגישות לתאריכי אבל; build+lint נקי</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D115"/>
+  <autoFilter ref="A1:D122"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D115"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D122"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D130</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D130"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2116,10 +2116,122 @@
         <v>BL-060: כל התאריכים החדשים עם religion: Secular; ברכות EN+HE; הערות רגישות לתאריכי אבל; build+lint נקי</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>✉️</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Sprint 11 — Quick Send (BL-064) + Auto-Regenerate on Tone (BL-063) + UpgradeScreen CTA Fix (BL-062)</v>
+      </c>
+      <c r="C123" t="str">
+        <v/>
+      </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>✉️</v>
+      </c>
+      <c r="B124" t="str">
+        <v>BL-063 / BUG-047: useEffect([tone]) — שינוי tier מחולל generate() מחדש אוטומטית ב-GreetingEditorScreen</v>
+      </c>
+      <c r="C124" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D124" t="str">
+        <v>BL-063 / BUG-047: useEffect([tone]) נוסף ל-GreetingEditorScreen — שינוי tier מפעיל generate() מחדש אוטומטית</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>✉️</v>
+      </c>
+      <c r="B125" t="str">
+        <v>BL-063 / BUG-048: תבניות עברית friendly תוקנו — "לברר"→"לדעת", "שכל טוב"→"שיהיה הכל טוב"</v>
+      </c>
+      <c r="C125" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D125" t="str">
+        <v>BL-063 / BUG-048: תבניות עברית friendly תוקנו — 'לברר'→'לדעת', 'שכל טוב'→'שיהיה הכל טוב'; business 'שלחתי ידו/ת'→'פניתי'</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>✉️</v>
+      </c>
+      <c r="B126" t="str">
+        <v>BL-062 / BUG-045: UpgradeScreen CTA — t("upgrade_cta") במקום t("payme_goPayMe"); גנרי ולא תלוי ספק</v>
+      </c>
+      <c r="C126" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D126" t="str">
+        <v>BL-062 / BUG-045: UpgradeScreen CTA עכשיו משתמש ב-t('upgrade_cta') — 'שדרג עכשיו' — לא תלוי ב-PayMe</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>✉️</v>
+      </c>
+      <c r="B127" t="str">
+        <v>BL-062 / BUG-046: upgrade_unlockEverything HE = "שדרג לפרמיום"; upgrade_cta EN/HE נוסף ל-i18n</v>
+      </c>
+      <c r="C127" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D127" t="str">
+        <v>BL-062 / BUG-046: upgrade_unlockEverything HE שונה ל-'שדרג לפרמיום'; upgrade_cta EN/HE נוסף ל-i18n</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>✉️</v>
+      </c>
+      <c r="B128" t="str">
+        <v>BL-064: כפתור "שלח ברכה" על כרטיסי ימי הולדת + קבוצה; premium → Quick Send; free → /greeting</v>
+      </c>
+      <c r="C128" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D128" t="str">
+        <v>BL-064: כפתור 'שלח ברכה' על כרטיסי ימי הולדת + כרטיסי קבוצה; premium → openQuickSend; free → navigate to /greeting</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>✉️</v>
+      </c>
+      <c r="B129" t="str">
+        <v>BL-064: Quick Send overlay — 3 options AI; WhatsApp/Copy/Open Editor לכל option; backdrop סגירה; copied feedback 2s</v>
+      </c>
+      <c r="C129" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D129" t="str">
+        <v>BL-064: Quick Send overlay — 3 options AI per contact; WhatsApp/Copy/Open Editor לכל option; backdrop סגירה; copiedIdx feedback 2s</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>✉️</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Sprint 11 QA: build נקי + lint נקי; BL-062, BL-063, BL-064 מאומתים</v>
+      </c>
+      <c r="C130" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Sprint 11 QA: build נקי + lint נקי; BL-062+063+064 מיושמים ומאומתים</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D122"/>
+  <autoFilter ref="A1:D130"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D122"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D130"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D138</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D138"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2228,10 +2228,122 @@
         <v>Sprint 11 QA: build נקי + lint נקי; BL-062+063+064 מיושמים ומאומתים</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>🪪</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Sprint 12 — Personal User Layer (BL-067) + AI Personalization MVP (BL-065)</v>
+      </c>
+      <c r="C131" t="str">
+        <v/>
+      </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>🪪</v>
+      </c>
+      <c r="B132" t="str">
+        <v>BL-067: userProfileService — getUserName/saveUserName/isProfileSetup; nm_user_name ב-localStorage</v>
+      </c>
+      <c r="C132" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D132" t="str">
+        <v>BL-067: userProfileService — getUserName/saveUserName/isProfileSetup; localStorage key nm_user_name</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>🪪</v>
+      </c>
+      <c r="B133" t="str">
+        <v>BL-067: UserSetupScreen — שאלת שם + CTA "יאללה נתחיל" + קישור דלג; מנווט ל-/dashboard</v>
+      </c>
+      <c r="C133" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D133" t="str">
+        <v>BL-067: UserSetupScreen — שאלת שם עם input, CTA 'יאללה נתחיל' + קישור דלג; מנווט ל-/dashboard אחרי שמירה</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>🪪</v>
+      </c>
+      <c r="B134" t="str">
+        <v>BL-067: App.tsx route /setup + redirect: onboarding→setup→dashboard לפי localStorage</v>
+      </c>
+      <c r="C134" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D134" t="str">
+        <v>BL-067: App.tsx — route /setup נוסף; redirect: onboarding→setup→dashboard לפי מצב localStorage</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>🪪</v>
+      </c>
+      <c r="B135" t="str">
+        <v>BL-067: Dashboard hero — "היי {name}" כשיש שם; pending count; כפתור "שלח ברכה עכשיו"</v>
+      </c>
+      <c r="C135" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D135" t="str">
+        <v>BL-067: DashboardScreen hero — 'היי {name}' כשיש שם; pending count בכותרת; כפתור 'שלח ברכה עכשיו' → openQuickSend/navigate</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>🪪</v>
+      </c>
+      <c r="B136" t="str">
+        <v>BL-067 UX: pending greetings panel — כל item קליקבילי → Quick Send (BL-064)</v>
+      </c>
+      <c r="C136" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D136" t="str">
+        <v>BL-067 UX req: pending items קליקביליים → פותחים Quick Send (BL-064); מוצגים כשיש pending ו-hasTodayHighlights=false</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>🪪</v>
+      </c>
+      <c r="B137" t="str">
+        <v>BL-065 MVP: PROFESSIONAL_RELATIONSHIPS → resolveTone מחזיר professional מינימום; VIP נשמר</v>
+      </c>
+      <c r="C137" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D137" t="str">
+        <v>BL-065 MVP: PROFESSIONAL_RELATIONSHIPS (client/business_partner/manager/employee/mentor) → resolveTone מחזיר professional מינימום; VIP נשמר; Dashboard + GreetingEditor</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>🪪</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Sprint 12 QA: build נקי + lint נקי; BL-067 + BL-065 מאומתים</v>
+      </c>
+      <c r="C138" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Sprint 12 QA: build נקי + lint נקי; BL-067 + BL-065 מיושמים ומאומתים</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D130"/>
+  <autoFilter ref="A1:D138"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D138"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D142</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D142"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2340,10 +2340,66 @@
         <v>Sprint 12 QA: build נקי + lint נקי; BL-067 + BL-065 מיושמים ומאומתים</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Bug Fixes &amp; Improvements — Sprint Suspension Mode</v>
+      </c>
+      <c r="C139" t="str">
+        <v/>
+      </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B140" t="str">
+        <v>RTL לוח שנה: חצים מוחלפים בעברית (prev=ימין, next=שמאל); LTR ללא שינוי</v>
+      </c>
+      <c r="C140" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D140" t="str">
+        <v>RTL calendar arrows: ChevronLeft/Right מוחלפים כשlang==='he'; prev button מימין, next משמאל בעברית; LTR — ללא שינוי</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B141" t="str">
+        <v>יום הולדת עברי: dropdown גמטריה; תצוגה כ״א בטבת; Hebrew+Gregorian — 2 אירועים עצמאיים</v>
+      </c>
+      <c r="C141" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Hebrew birthday: day dropdown מציג גמטריה (א–ל); תצוגה בפורמט כ״א בטבת ב-ContactDetailScreen; Hebrew+Gregorian מטופלים כ-2 אירועים עצמאיים בלוח השנה</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B142" t="str">
+        <v>BUG-049: PaymeScreen demo mode — באנר הדגמה + כפתור הפעל פרימיום; לא נדרש תשלום אמיתי</v>
+      </c>
+      <c r="C142" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D142" t="str">
+        <v>BUG-049: PaymeScreen שוכתב כ-demo mode; באנר 'זוהי גרסת הדגמה'; כפתור 'הפעל פרימיום (הדגמה)' → activatePremium() + navigate('/dashboard'); build+lint ✅</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D138"/>
+  <autoFilter ref="A1:D142"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D138"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D142"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D145</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D145"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2396,10 +2396,52 @@
         <v>BUG-049: PaymeScreen שוכתב כ-demo mode; באנר 'זוהי גרסת הדגמה'; כפתור 'הפעל פרימיום (הדגמה)' → activatePremium() + navigate('/dashboard'); build+lint ✅</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B143" t="str">
+        <v>BUG-059: Google Translate — translate=no + notranslate על html ו-root מונעים תרגום אוטומטי</v>
+      </c>
+      <c r="C143" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D143" t="str">
+        <v>BUG-059 תוקן — translate=no + notranslate על html/root מונעים Google Translate</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B144" t="str">
+        <v>BUG-060: תיאורי חגים בעברית — heDescription ב-46 חגים; HolidayDetailScreen מציג עברית כשheLang</v>
+      </c>
+      <c r="C144" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D144" t="str">
+        <v>BUG-060 תוקן — heDescription הוסף לכל 46 חגים; HolidayDetailScreen מציג עברית כששפה=he</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B145" t="str">
+        <v>BUG-061: קבוצות — רשימת חגים ללא כפילויות; שמות עבריים; דת מתורגמת</v>
+      </c>
+      <c r="C145" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D145" t="str">
+        <v>BUG-061 תוקן — GroupsScreen מציג חג ייחודי אחד (ללא כפילות שנה), שם עברי כשhe, דת מתורגמת</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D142"/>
+  <autoFilter ref="A1:D145"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D142"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D145"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D148</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D148"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2438,10 +2438,52 @@
         <v>BUG-061 תוקן — GroupsScreen מציג חג ייחודי אחד (ללא כפילות שנה), שם עברי כשhe, דת מתורגמת</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B146" t="str">
+        <v>BUG-074: Input — מיקום אייקון RTL-aware (ימין בעברית, שמאל באנגלית); ריפוד מותאם</v>
+      </c>
+      <c r="C146" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D146" t="str">
+        <v>BUG-074 תוקן — Input.tsx: useLang + isRTL; אייקון ב-right-3/left-3 בהתאם לכיוון; ריפוד pr-10/pl-10 מתאים. build+lint ✅</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B147" t="str">
+        <v>BUG-075: PrivacyScreen — 10 סעיפים + hero/badge/intro/footer מתורגמים לעברית (25 מפתחות i18n)</v>
+      </c>
+      <c r="C147" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D147" t="str">
+        <v>BUG-075 תוקן — PrivacyScreen: SECTIONS הועבר לתוך הקומפוננטה; 25 מפתחות i18n חדשים (EN+HE) לכל הכותרות, גוף הטקסט, hero, badge, intro, footer. build+lint ✅</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B148" t="str">
+        <v>BUG-076: מחלקות CSS פיזיות (ml-*/mr-*/text-right) הוחלפו במחלקות לוגיות (ms-*/me-*/text-end) ב-6 קבצים</v>
+      </c>
+      <c r="C148" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D148" t="str">
+        <v>BUG-076 תוקן — מחלקות CSS פיזיות (ml-*/mr-*/text-right) הוחלפו במחלקות לוגיות (ms-*/me-*/text-end) ב-BirthdayGreetingEditorScreen, App.tsx, DashboardScreen, MediaAttachmentPicker, GreetingEditorScreen, WhatsNewScreen, CalendarScreen. build+lint ✅</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D145"/>
+  <autoFilter ref="A1:D148"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D148"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D150</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D150"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2480,10 +2480,38 @@
         <v>BUG-076 תוקן — מחלקות CSS פיזיות (ml-*/mr-*/text-right) הוחלפו במחלקות לוגיות (ms-*/me-*/text-end) ב-BirthdayGreetingEditorScreen, App.tsx, DashboardScreen, MediaAttachmentPicker, GreetingEditorScreen, WhatsNewScreen, CalendarScreen. build+lint ✅</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B149" t="str">
+        <v>BUG-077: WhatsApp emoji encoding — אומת: encodeURIComponent קיים ב-buildWhatsAppUrl; כל נתיבי השליחה מוסדרים דרכו</v>
+      </c>
+      <c r="C149" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D149" t="str">
+        <v>BUG-077 אומת — buildWhatsAppUrl משתמש ב-encodeURIComponent; כל נתיבי WhatsApp (ChannelPicker, WhatsAppButton, DashboardScreen) עוברים דרך openWhatsApp → buildWhatsAppUrl. אין שינוי קוד נדרש.</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B150" t="str">
+        <v>BUG-078: Voice message — Modal "צירוף ידני" מוצג לאחר פתיחת WhatsApp כשיש הקלטה; RTL; נשאר עד סגירה ידנית</v>
+      </c>
+      <c r="C150" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D150" t="str">
+        <v>BUG-078 תוקן — Modal הקלטה קולית נוסף ל-ChannelPicker ו-WhatsAppButton; מופיע לאחר פתיחת WhatsApp כשmedia.type===audio; נשאר עד סגירה ידנית; RTL; 2 מפתחות i18n (EN+HE). build+lint ✅</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D148"/>
+  <autoFilter ref="A1:D150"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D148"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D150"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D152</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D152"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2508,10 +2508,38 @@
         <v>BUG-078 תוקן — Modal הקלטה קולית נוסף ל-ChannelPicker ו-WhatsAppButton; מופיע לאחר פתיחת WhatsApp כשmedia.type===audio; נשאר עד סגירה ידנית; RTL; 2 מפתחות i18n (EN+HE). build+lint ✅</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B151" t="str">
+        <v>BUG-079: 14 חגים יהודיים חסרים נוספו — ל"ג בעומר, שמחת תורה, תשעה באב, י"ז בתמוז, י' בטבת, תענית אסתר, צום גדליה (2025+2026); hebcalDate(); type fast/minor/major</v>
+      </c>
+      <c r="C151" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D151" t="str">
+        <v>BUG-079 תוקן — 14 רשומות חגים יהודיים חסרים נוספו ל-holidays.ts: ל"ג בעומר, שמחת תורה, תשעה באב, י"ז בתמוז, י' בטבת, תענית אסתר, צום גדליה — 2 שנים לכל חג; hebcalDate() לתאריכים מדויקים; type: fast/minor/major; EN+HE. build+lint ✅</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>🐞</v>
+      </c>
+      <c r="B152" t="str">
+        <v>BUG-080: כפילויות חגים ב-Event Type dropdown — useMemo dedup by name (upcoming-first) ב-GreetingEditorScreen</v>
+      </c>
+      <c r="C152" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D152" t="str">
+        <v>BUG-080 תוקן — GreetingEditorScreen: useMemo dedup holidays by name (upcoming-first) — כל חג מופיע פעם אחת בתפריט Event Type. build+lint ✅</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D150"/>
+  <autoFilter ref="A1:D152"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D152"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D154</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D152"/>
+  <dimension ref="A1:D154"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2536,10 +2536,38 @@
         <v>BUG-080 תוקן — GreetingEditorScreen: useMemo dedup holidays by name (upcoming-first) — כל חג מופיע פעם אחת בתפריט Event Type. build+lint ✅</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>⚡</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Sprint 14 — חגים דינמיים BL-077 (Hebcal)</v>
+      </c>
+      <c r="C153" t="str">
+        <v/>
+      </c>
+      <c r="D153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>⚡</v>
+      </c>
+      <c r="B154" t="str">
+        <v>BL-077: חגים יהודיים דינמיים — 17 תבניות Hebcal; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
+      </c>
+      <c r="C154" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D154" t="str">
+        <v>BL-077 הושלם — חגים יהודיים נוצרים דינמית ע״י @hebcal/core; 17 תבניות; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D152"/>
+  <autoFilter ref="A1:D154"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D152"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D154"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D158</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D158"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2564,10 +2564,66 @@
         <v>BL-077 הושלם — חגים יהודיים נוצרים דינמית ע״י @hebcal/core; 17 תבניות; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>📥</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Sprint 15 — ייבוא אנשי קשר UX: BL-046, BL-047, BL-048</v>
+      </c>
+      <c r="C155" t="str">
+        <v/>
+      </c>
+      <c r="D155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>📥</v>
+      </c>
+      <c r="B156" t="str">
+        <v>BL-046: כפתור ייבוא אנשי קשר מוצג בכרטיסיית אנשי קשר לכל המשתמשים; גייט Premium נשמר בנתיב /import</v>
+      </c>
+      <c r="C156" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D156" t="str">
+        <v>BL-046 תוקן — כפתור ייבוא בכרטיסיית אנשי קשר מוצג לכל המשתמשים; גייט Premium נשמר בנתיב</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>📥</v>
+      </c>
+      <c r="B157" t="str">
+        <v>BL-047: תווית "כרגע ניתן לייבא קובץ CSV בלבד" מוצגת ליד אזור ההעלאה ב-ImportContactsScreen; תרגום עברי קיים</v>
+      </c>
+      <c r="C157" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D157" t="str">
+        <v>BL-047 אומת — תווית CSV בלבד מוצגת ליד אזור ההעלאה; תרגום עברי קיים</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>📥</v>
+      </c>
+      <c r="B158" t="str">
+        <v>BL-048: כרטיסיית ייבוא ממכשיר (גרדיאנט כחול, סמארטפון) מוצגת בראש ImportContactsScreen; נגישות ויזואלית מלאה</v>
+      </c>
+      <c r="C158" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D158" t="str">
+        <v>BL-048 אומת — כרטיסיית ייבוא ממכשיר מוצגת בראש המסך עם גרדיאנט כחול ואייקון סמארטפון</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D154"/>
+  <autoFilter ref="A1:D158"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D158"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D160</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D160"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2620,10 +2620,38 @@
         <v>BL-048 אומת — כרטיסיית ייבוא ממכשיר מוצגת בראש המסך עם גרדיאנט כחול ואייקון סמארטפון</v>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>👤</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Sprint 16 — שכבת משתמש אישית BL-067: UserSetupScreen, dashboard_hello, pendingItems</v>
+      </c>
+      <c r="C159" t="str">
+        <v/>
+      </c>
+      <c r="D159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>👤</v>
+      </c>
+      <c r="B160" t="str">
+        <v>BL-067: UserSetupScreen first-launch, nm_user_name persist, dashboard_hello/pending/first_greeting EN+HE, pendingItems clickable, empty states graceful; DoD מלא ✅</v>
+      </c>
+      <c r="C160" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D160" t="str">
+        <v>BL-067 DoD מלא אומת — UserSetupScreen first-launch, nm_user_name persist, dashboard_hello/pending/first_greeting keys EN+HE, pendingItems clickable, empty states graceful</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D158"/>
+  <autoFilter ref="A1:D160"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D158"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D160"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D161</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D161"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2538,16 +2538,16 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>⚡</v>
+        <v>🐞</v>
       </c>
       <c r="B153" t="str">
-        <v>Sprint 14 — חגים דינמיים BL-077 (Hebcal)</v>
+        <v>BUG-081: showPremiumUI=!TEMP_PREMIUM_UNLOCK — Crown + "פרמיום" מוסתרים ב-ContactForm ו-Settings כשגייט MVP פתוח; הפיכה ל-false משחזרת הכל</v>
       </c>
       <c r="C153" t="str">
-        <v/>
+        <v>✅</v>
       </c>
       <c r="D153" t="str">
-        <v/>
+        <v>BUG-081 תוקן — showPremiumUI=!TEMP_PREMIUM_UNLOCK; Crown+פרמיום מוסתרים ב-ContactForm ו-Settings; build+lint ✅</v>
       </c>
     </row>
     <row r="154">
@@ -2555,27 +2555,27 @@
         <v>⚡</v>
       </c>
       <c r="B154" t="str">
-        <v>BL-077: חגים יהודיים דינמיים — 17 תבניות Hebcal; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
+        <v>Sprint 14 — חגים דינמיים BL-077 (Hebcal)</v>
       </c>
       <c r="C154" t="str">
-        <v>✅</v>
+        <v/>
       </c>
       <c r="D154" t="str">
-        <v>BL-077 הושלם — חגים יהודיים נוצרים דינמית ע״י @hebcal/core; 17 תבניות; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
+        <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>📥</v>
+        <v>⚡</v>
       </c>
       <c r="B155" t="str">
-        <v>Sprint 15 — ייבוא אנשי קשר UX: BL-046, BL-047, BL-048</v>
+        <v>BL-077: חגים יהודיים דינמיים — 17 תבניות Hebcal; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
       </c>
       <c r="C155" t="str">
-        <v/>
+        <v>✅</v>
       </c>
       <c r="D155" t="str">
-        <v/>
+        <v>BL-077 הושלם — חגים יהודיים נוצרים דינמית ע״י @hebcal/core; 17 תבניות; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
       </c>
     </row>
     <row r="156">
@@ -2583,13 +2583,13 @@
         <v>📥</v>
       </c>
       <c r="B156" t="str">
-        <v>BL-046: כפתור ייבוא אנשי קשר מוצג בכרטיסיית אנשי קשר לכל המשתמשים; גייט Premium נשמר בנתיב /import</v>
+        <v>Sprint 15 — ייבוא אנשי קשר UX: BL-046, BL-047, BL-048</v>
       </c>
       <c r="C156" t="str">
-        <v>✅</v>
+        <v/>
       </c>
       <c r="D156" t="str">
-        <v>BL-046 תוקן — כפתור ייבוא בכרטיסיית אנשי קשר מוצג לכל המשתמשים; גייט Premium נשמר בנתיב</v>
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -2597,13 +2597,13 @@
         <v>📥</v>
       </c>
       <c r="B157" t="str">
-        <v>BL-047: תווית "כרגע ניתן לייבא קובץ CSV בלבד" מוצגת ליד אזור ההעלאה ב-ImportContactsScreen; תרגום עברי קיים</v>
+        <v>BL-046: כפתור ייבוא אנשי קשר מוצג בכרטיסיית אנשי קשר לכל המשתמשים; גייט Premium נשמר בנתיב /import</v>
       </c>
       <c r="C157" t="str">
         <v>✅</v>
       </c>
       <c r="D157" t="str">
-        <v>BL-047 אומת — תווית CSV בלבד מוצגת ליד אזור ההעלאה; תרגום עברי קיים</v>
+        <v>BL-046 תוקן — כפתור ייבוא בכרטיסיית אנשי קשר מוצג לכל המשתמשים; גייט Premium נשמר בנתיב</v>
       </c>
     </row>
     <row r="158">
@@ -2611,27 +2611,27 @@
         <v>📥</v>
       </c>
       <c r="B158" t="str">
-        <v>BL-048: כרטיסיית ייבוא ממכשיר (גרדיאנט כחול, סמארטפון) מוצגת בראש ImportContactsScreen; נגישות ויזואלית מלאה</v>
+        <v>BL-047: תווית "כרגע ניתן לייבא קובץ CSV בלבד" מוצגת ליד אזור ההעלאה ב-ImportContactsScreen; תרגום עברי קיים</v>
       </c>
       <c r="C158" t="str">
         <v>✅</v>
       </c>
       <c r="D158" t="str">
-        <v>BL-048 אומת — כרטיסיית ייבוא ממכשיר מוצגת בראש המסך עם גרדיאנט כחול ואייקון סמארטפון</v>
+        <v>BL-047 אומת — תווית CSV בלבד מוצגת ליד אזור ההעלאה; תרגום עברי קיים</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>👤</v>
+        <v>📥</v>
       </c>
       <c r="B159" t="str">
-        <v>Sprint 16 — שכבת משתמש אישית BL-067: UserSetupScreen, dashboard_hello, pendingItems</v>
+        <v>BL-048: כרטיסיית ייבוא ממכשיר (גרדיאנט כחול, סמארטפון) מוצגת בראש ImportContactsScreen; נגישות ויזואלית מלאה</v>
       </c>
       <c r="C159" t="str">
-        <v/>
+        <v>✅</v>
       </c>
       <c r="D159" t="str">
-        <v/>
+        <v>BL-048 אומת — כרטיסיית ייבוא ממכשיר מוצגת בראש המסך עם גרדיאנט כחול ואייקון סמארטפון</v>
       </c>
     </row>
     <row r="160">
@@ -2639,19 +2639,33 @@
         <v>👤</v>
       </c>
       <c r="B160" t="str">
+        <v>Sprint 16 — שכבת משתמש אישית BL-067: UserSetupScreen, dashboard_hello, pendingItems</v>
+      </c>
+      <c r="C160" t="str">
+        <v/>
+      </c>
+      <c r="D160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>👤</v>
+      </c>
+      <c r="B161" t="str">
         <v>BL-067: UserSetupScreen first-launch, nm_user_name persist, dashboard_hello/pending/first_greeting EN+HE, pendingItems clickable, empty states graceful; DoD מלא ✅</v>
       </c>
-      <c r="C160" t="str">
-        <v>✅</v>
-      </c>
-      <c r="D160" t="str">
+      <c r="C161" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D161" t="str">
         <v>BL-067 DoD מלא אומת — UserSetupScreen first-launch, nm_user_name persist, dashboard_hello/pending/first_greeting keys EN+HE, pendingItems clickable, empty states graceful</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D160"/>
+  <autoFilter ref="A1:D161"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D160"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D161"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D162</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D162"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2552,16 +2552,16 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>⚡</v>
+        <v>🐞</v>
       </c>
       <c r="B154" t="str">
-        <v>Sprint 14 — חגים דינמיים BL-077 (Hebcal)</v>
+        <v>BL-080/BUG-082: parseDateLocal() מחליף new Date(string) — מונע הסטת UTC ב-Asia/Jerusalem; safeguards לתאריך חסר/לא תקין; Hebcal Israel mode אומת כנכון</v>
       </c>
       <c r="C154" t="str">
-        <v/>
+        <v>✅</v>
       </c>
       <c r="D154" t="str">
-        <v/>
+        <v>BL-080 תוקן — parseDateLocal() מונע הסטת UTC; safeguards לתאריך חסר; build+lint ✅</v>
       </c>
     </row>
     <row r="155">
@@ -2569,27 +2569,27 @@
         <v>⚡</v>
       </c>
       <c r="B155" t="str">
-        <v>BL-077: חגים יהודיים דינמיים — 17 תבניות Hebcal; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
+        <v>Sprint 14 — חגים דינמיים BL-077 (Hebcal)</v>
       </c>
       <c r="C155" t="str">
-        <v>✅</v>
+        <v/>
       </c>
       <c r="D155" t="str">
-        <v>BL-077 הושלם — חגים יהודיים נוצרים דינמית ע״י @hebcal/core; 17 תבניות; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
+        <v/>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>📥</v>
+        <v>⚡</v>
       </c>
       <c r="B156" t="str">
-        <v>Sprint 15 — ייבוא אנשי קשר UX: BL-046, BL-047, BL-048</v>
+        <v>BL-077: חגים יהודיים דינמיים — 17 תבניות Hebcal; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
       </c>
       <c r="C156" t="str">
-        <v/>
+        <v>✅</v>
       </c>
       <c r="D156" t="str">
-        <v/>
+        <v>BL-077 הושלם — חגים יהודיים נוצרים דינמית ע״י @hebcal/core; 17 תבניות; YEAR_RANGE=[שנה-1..שנה+2]; IDs ו-Holiday interface זהים; build+lint ✅</v>
       </c>
     </row>
     <row r="157">
@@ -2597,13 +2597,13 @@
         <v>📥</v>
       </c>
       <c r="B157" t="str">
-        <v>BL-046: כפתור ייבוא אנשי קשר מוצג בכרטיסיית אנשי קשר לכל המשתמשים; גייט Premium נשמר בנתיב /import</v>
+        <v>Sprint 15 — ייבוא אנשי קשר UX: BL-046, BL-047, BL-048</v>
       </c>
       <c r="C157" t="str">
-        <v>✅</v>
+        <v/>
       </c>
       <c r="D157" t="str">
-        <v>BL-046 תוקן — כפתור ייבוא בכרטיסיית אנשי קשר מוצג לכל המשתמשים; גייט Premium נשמר בנתיב</v>
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -2611,13 +2611,13 @@
         <v>📥</v>
       </c>
       <c r="B158" t="str">
-        <v>BL-047: תווית "כרגע ניתן לייבא קובץ CSV בלבד" מוצגת ליד אזור ההעלאה ב-ImportContactsScreen; תרגום עברי קיים</v>
+        <v>BL-046: כפתור ייבוא אנשי קשר מוצג בכרטיסיית אנשי קשר לכל המשתמשים; גייט Premium נשמר בנתיב /import</v>
       </c>
       <c r="C158" t="str">
         <v>✅</v>
       </c>
       <c r="D158" t="str">
-        <v>BL-047 אומת — תווית CSV בלבד מוצגת ליד אזור ההעלאה; תרגום עברי קיים</v>
+        <v>BL-046 תוקן — כפתור ייבוא בכרטיסיית אנשי קשר מוצג לכל המשתמשים; גייט Premium נשמר בנתיב</v>
       </c>
     </row>
     <row r="159">
@@ -2625,27 +2625,27 @@
         <v>📥</v>
       </c>
       <c r="B159" t="str">
-        <v>BL-048: כרטיסיית ייבוא ממכשיר (גרדיאנט כחול, סמארטפון) מוצגת בראש ImportContactsScreen; נגישות ויזואלית מלאה</v>
+        <v>BL-047: תווית "כרגע ניתן לייבא קובץ CSV בלבד" מוצגת ליד אזור ההעלאה ב-ImportContactsScreen; תרגום עברי קיים</v>
       </c>
       <c r="C159" t="str">
         <v>✅</v>
       </c>
       <c r="D159" t="str">
-        <v>BL-048 אומת — כרטיסיית ייבוא ממכשיר מוצגת בראש המסך עם גרדיאנט כחול ואייקון סמארטפון</v>
+        <v>BL-047 אומת — תווית CSV בלבד מוצגת ליד אזור ההעלאה; תרגום עברי קיים</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>👤</v>
+        <v>📥</v>
       </c>
       <c r="B160" t="str">
-        <v>Sprint 16 — שכבת משתמש אישית BL-067: UserSetupScreen, dashboard_hello, pendingItems</v>
+        <v>BL-048: כרטיסיית ייבוא ממכשיר (גרדיאנט כחול, סמארטפון) מוצגת בראש ImportContactsScreen; נגישות ויזואלית מלאה</v>
       </c>
       <c r="C160" t="str">
-        <v/>
+        <v>✅</v>
       </c>
       <c r="D160" t="str">
-        <v/>
+        <v>BL-048 אומת — כרטיסיית ייבוא ממכשיר מוצגת בראש המסך עם גרדיאנט כחול ואייקון סמארטפון</v>
       </c>
     </row>
     <row r="161">
@@ -2653,19 +2653,33 @@
         <v>👤</v>
       </c>
       <c r="B161" t="str">
+        <v>Sprint 16 — שכבת משתמש אישית BL-067: UserSetupScreen, dashboard_hello, pendingItems</v>
+      </c>
+      <c r="C161" t="str">
+        <v/>
+      </c>
+      <c r="D161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>👤</v>
+      </c>
+      <c r="B162" t="str">
         <v>BL-067: UserSetupScreen first-launch, nm_user_name persist, dashboard_hello/pending/first_greeting EN+HE, pendingItems clickable, empty states graceful; DoD מלא ✅</v>
       </c>
-      <c r="C161" t="str">
-        <v>✅</v>
-      </c>
-      <c r="D161" t="str">
+      <c r="C162" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D162" t="str">
         <v>BL-067 DoD מלא אומת — UserSetupScreen first-launch, nm_user_name persist, dashboard_hello/pending/first_greeting keys EN+HE, pendingItems clickable, empty states graceful</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D161"/>
+  <autoFilter ref="A1:D162"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D161"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D162"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/NeverMiss_QA_Checklist.xlsx
+++ b/NeverMiss_QA_Checklist.xlsx
@@ -6,7 +6,7 @@
     <sheet name="QA Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'QA Checklist'!A1:D184</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D162"/>
+  <dimension ref="A1:D184"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -2676,10 +2676,318 @@
         <v>BL-067 DoD מלא אומת — UserSetupScreen first-launch, nm_user_name persist, dashboard_hello/pending/first_greeting keys EN+HE, pendingItems clickable, empty states graceful</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>🔧</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Sprint 17 — BL-075: תיקוני BugHunter</v>
+      </c>
+      <c r="C163" t="str">
+        <v/>
+      </c>
+      <c r="D163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>📱</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Sprint 18 — RTL icons, contact card overflow, BottomNav active indicator</v>
+      </c>
+      <c r="C164" t="str">
+        <v/>
+      </c>
+      <c r="D164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>📱</v>
+      </c>
+      <c r="B165" t="str">
+        <v>BL-081: ImportContactsScreen — 3 ArrowRight הוחלפו ב-lang==="he" ? ArrowLeft : ArrowRight; כפתור מכשיר, הורד תבנית, עמודת מיפוי כולם RTL-נכון</v>
+      </c>
+      <c r="C165" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D165" t="str">
+        <v>BL-081 תוקן — ImportContactsScreen: 3 מופעי ArrowRight הוחלפו ב-lang==='he' ? ArrowLeft : ArrowRight; useLang() נוסף; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>📱</v>
+      </c>
+      <c r="B166" t="str">
+        <v>BL-075: ContactCard — 3-dot MoreVertical menu; Edit מנווט לטופס; Delete פותח confirm modal; סגירה על-ידי outside click + Escape; aria-label; dropdown RTL-aware</v>
+      </c>
+      <c r="C166" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D166" t="str">
+        <v>BL-075 יושם — ContactCard: 3-dot MoreVertical menu עם Edit+Delete; close on outside click + Escape; delete confirmation modal; aria-label contacts_moreOptions; RTL-correct dropdown position; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>📱</v>
+      </c>
+      <c r="B167" t="str">
+        <v>BL-049: BottomNav active tab — box-shadow inset 0 2px 0 var(--color-primary) + opacity-20 icon glow; active tab ברור ומובחן; ללא רגרסיה</v>
+      </c>
+      <c r="C167" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D167" t="str">
+        <v>BL-049 שופר — BottomNav active tab: box-shadow inset 0 2px 0 var(--color-primary) נוסף; opacity-20 (מ-15); active indication ברור יותר; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>🌐</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Sprint 19 — BL-079: Language-Religion drilldown + CSV localization</v>
+      </c>
+      <c r="C168" t="str">
+        <v/>
+      </c>
+      <c r="D168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>🌐</v>
+      </c>
+      <c r="B169" t="str">
+        <v>BL-079: contactConfig.ts single source of truth; normalizeLanguage/normalizeReligion מקבלים raw key / EN label / HE label; CSV template מלוקלי לפי app lang; Religion dropdown ב-ContactForm מסודר לפי שפת הקשר; build+lint ✅</v>
+      </c>
+      <c r="C169" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D169" t="str">
+        <v>BL-079 יושם — contactConfig.ts: LANGUAGE_KEYS/RELIGION_KEYS/LANGUAGE_RELIGION_ORDER/normalizeLanguage/normalizeReligion/getLanguageDisplayValue/getReligionDisplayValue; importService.ts: normalizeLanguage+normalizeReligion במקום cast ישיר; ImportContactsScreen.tsx: CSV headers+example row מלוקלים לפי lang; ContactFormScreen.tsx: Religion dropdown מסודר לפי LANGUAGE_RELIGION_ORDER; build+lint ✅; normalization tests ✅</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>📅</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Sprint 20 — BL-076: Hebrew Birthday import/export round-trip</v>
+      </c>
+      <c r="C170" t="str">
+        <v/>
+      </c>
+      <c r="D170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>📅</v>
+      </c>
+      <c r="B171" t="str">
+        <v>BL-076: Hebrew Birthday column בתבנית CSV (EN+HE); DETECTABLE_FIELDS: hebrewBirthday לפני birthday; processImport כותב hebrewBirthday; round-trip export↔import תקין; build+lint ✅</v>
+      </c>
+      <c r="C171" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D171" t="str">
+        <v>BL-076 יושם — importService.ts: hebrewBirthday ב-DETECTABLE_FIELDS (לפני birthday) + processImport; ImportContactsScreen.tsx: עמודת Hebrew Birthday (DD-MM) בתבנית EN+HE; round-trip export↔import תקין; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>👥</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Sprint 21 — BL-084/082/068/069: Import fix, Score tooltip, Group members, Assign group</v>
+      </c>
+      <c r="C172" t="str">
+        <v/>
+      </c>
+      <c r="D172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>👥</v>
+      </c>
+      <c r="B173" t="str">
+        <v>BL-084: normalizeBirthday() ב-importService.ts; isNaN guard ב-ContactDetailScreen.tsx; קשר מיובא עם תאריך לא-ISO נפתח ללא קריסה; build+lint ✅</v>
+      </c>
+      <c r="C173" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D173" t="str">
+        <v>BL-084 תוקן — normalizeBirthday() ב-importService.ts; isNaN guard ב-ContactDetailScreen.tsx; מונע קריסה על תאריכים בפורמט שגוי; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>👥</v>
+      </c>
+      <c r="B174" t="str">
+        <v>BL-082: תג ציון ב-ContactCard הפך ל-button; לחיצה מציגה tooltip עם הסבר ציון; click-outside/Escape סוגרים; EN+HE; build+lint ✅</v>
+      </c>
+      <c r="C174" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D174" t="str">
+        <v>BL-082 יושם — תג הציון ב-ContactCard הפך ל-button; tooltip עם score_tipTitle/score_tipBody בלחיצה; EN+HE; click-outside סוגר; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>👥</v>
+      </c>
+      <c r="B175" t="str">
+        <v>BL-068: contact picker ב-GroupsScreen modal (Premium); selectedContactIds נשמרים ב-handleSave; חיפוש אנשי קשר; EN+HE; build+lint ✅</v>
+      </c>
+      <c r="C175" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D175" t="str">
+        <v>BL-068 יושם — contact picker ב-GroupsScreen modal; selectedContactIds state; openForm מאתחל מ-group.contactIds; handleSave שומר; EN+HE; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>👥</v>
+      </c>
+      <c r="B176" t="str">
+        <v>BL-069: group selector ב-ContactFormScreen לאנשי קשר חדשים; לאחר addContact מעדכן group.contactIds; EN+HE; build+lint ✅</v>
+      </c>
+      <c r="C176" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D176" t="str">
+        <v>BL-069 יושם — group selector ב-ContactFormScreen (חדש בלבד); לאחר addContact מעדכן group.contactIds; EN+HE; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>📦</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Sprint 22 — BL-092/090/091: Import celebrationType + hebrewBirthday + export warning</v>
+      </c>
+      <c r="C177" t="str">
+        <v/>
+      </c>
+      <c r="D177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>📦</v>
+      </c>
+      <c r="B178" t="str">
+        <v>BL-092: celebrationType ב-DETECTABLE_FIELDS; normalizeCelebrationType(); processImport כותב celebrationType; round-trip export-import תקין; build+lint ✅</v>
+      </c>
+      <c r="C178" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D178" t="str">
+        <v>BL-092 יושם — celebrationType ב-DETECTABLE_FIELDS; normalizeCelebrationType() ממפה ערכים; processImport כותב celebrationType; round-trip export-import תקין; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>📦</v>
+      </c>
+      <c r="B179" t="str">
+        <v>BL-090: normalizeHebrewBirthday() מאמת DD-MM בייבוא; regex guard ב-ContactDetailScreen; ערכים לא תקינים לא מוצגים; build+lint ✅</v>
+      </c>
+      <c r="C179" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D179" t="str">
+        <v>BL-090 יושם — normalizeHebrewBirthday() מאמת פורמט DD-MM בייבוא; regex guard ב-ContactDetailScreen מונע הצגת ערך לא תקין; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>📦</v>
+      </c>
+      <c r="B180" t="str">
+        <v>BL-091: settings_exportGroupWarning EN+HE; אזהרה מתחת לכפתור ייצוא CSV ב-SettingsScreen; build+lint ✅</v>
+      </c>
+      <c r="C180" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D180" t="str">
+        <v>BL-091 יושם — settings_exportGroupWarning EN+HE; טקסט אזהרה מתחת לכפתור ייצוא CSV ב-SettingsScreen; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>🧹</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Sprint 23 — BL-086/088/087: Group delete cleanup, subtitle fix, group filter chip</v>
+      </c>
+      <c r="C181" t="str">
+        <v/>
+      </c>
+      <c r="D181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>🧹</v>
+      </c>
+      <c r="B182" t="str">
+        <v>BL-086: deleteContact מנקה contactIds בקבוצות; שלמות נתונים נשמרת; build+lint ✅</v>
+      </c>
+      <c r="C182" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D182" t="str">
+        <v>BL-086 תוקן — deleteContact ב-AppContext.tsx מנקה כעת contactIds בכל קבוצה שמכילה את המזהה שנמחק; שלמות נתונים נשמרת; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>🧹</v>
+      </c>
+      <c r="B183" t="str">
+        <v>BL-088: כותרת משנה ב-ContactsScreen — contacts_contact/contacts_contacts EN+HE; תיקון מפתחות i18n; build+lint ✅</v>
+      </c>
+      <c r="C183" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D183" t="str">
+        <v>BL-088 תוקן — כותרת המשנה ב-ContactsScreen מציגה 'X אנשי קשר' במקום 'X קבוצות'; מפתחות contacts_contact/contacts_contacts EN+HE; build+lint ✅</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>🧹</v>
+      </c>
+      <c r="B184" t="str">
+        <v>BL-087: chip סינון קבוצה ב-ContactsScreen; ?group=X מסנן + מציג chip; כפתור ניקוי; build+lint ✅</v>
+      </c>
+      <c r="C184" t="str">
+        <v>✅</v>
+      </c>
+      <c r="D184" t="str">
+        <v>BL-087 יושם — chip סינון קבוצה ב-ContactsScreen: מוצג כש-?group=X; שם הקבוצה + אמוג'י + כפתור ניקוי; הרשימה מסוננת; build+lint ✅</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D162"/>
+  <autoFilter ref="A1:D184"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D162"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D184"/>
   </ignoredErrors>
 </worksheet>
 </file>